--- a/clustering/8 subclusters (factoriescap_s (usage) 0).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (usage) 0).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
   <si>
     <t>clust</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>Во сколько раз субкластер из верхней половины factoriescap_s превосходит показатель нижнего</t>
+  </si>
+  <si>
+    <t>Медианы кластеров</t>
   </si>
 </sst>
 </file>
@@ -71,7 +74,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,6 +92,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -128,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -140,6 +152,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -445,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -780,6 +795,96 @@
       <c r="E20" s="4">
         <f t="shared" si="3"/>
         <v>3.6381909547738731</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2">
+        <v>337263.2171999964</v>
+      </c>
+      <c r="C24" s="2">
+        <v>190.99999999999821</v>
+      </c>
+      <c r="D24" s="2">
+        <v>7.9999999999999636</v>
+      </c>
+      <c r="E24" s="2">
+        <v>33.999999999999943</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>1</v>
+      </c>
+      <c r="B25" s="2">
+        <v>42894830.778399996</v>
+      </c>
+      <c r="C25" s="2">
+        <v>17079</v>
+      </c>
+      <c r="D25" s="2">
+        <v>718</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>2</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2172851.712599996</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2182</v>
+      </c>
+      <c r="D26" s="2">
+        <v>75.999999999999957</v>
+      </c>
+      <c r="E26" s="2">
+        <v>383.99999999999972</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>3</v>
+      </c>
+      <c r="B27" s="2">
+        <v>4317554.7359999968</v>
+      </c>
+      <c r="C27" s="2">
+        <v>4499</v>
+      </c>
+      <c r="D27" s="2">
+        <v>233</v>
+      </c>
+      <c r="E27" s="2">
+        <v>796.99999999999966</v>
       </c>
     </row>
   </sheetData>
